--- a/usuarios.xlsx
+++ b/usuarios.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jemarulandal\Desktop\ARCHIVOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jemarulandal\Desktop\vscode\selenium_prueba\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="15">
   <si>
     <t>Correo</t>
   </si>
@@ -66,42 +66,6 @@
   </si>
   <si>
     <t>Manila2036</t>
-  </si>
-  <si>
-    <t>Alejandra1</t>
-  </si>
-  <si>
-    <t>Alejandra2</t>
-  </si>
-  <si>
-    <t>Alejandra3</t>
-  </si>
-  <si>
-    <t>Alejandra4</t>
-  </si>
-  <si>
-    <t>Alejandra5</t>
-  </si>
-  <si>
-    <t>Alejandra6</t>
-  </si>
-  <si>
-    <t>Alejandra7</t>
-  </si>
-  <si>
-    <t>Alejandra8</t>
-  </si>
-  <si>
-    <t>Alejandra9</t>
-  </si>
-  <si>
-    <t>Alejandra10</t>
-  </si>
-  <si>
-    <t>Alejandra11</t>
-  </si>
-  <si>
-    <t>Alejandra12</t>
   </si>
   <si>
     <t>alejandra1@gmail.com</t>
@@ -488,11 +452,11 @@
       <c r="D1" s="3"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>14</v>
+      <c r="A2" s="2">
+        <v>1056123119</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>2</v>
@@ -500,11 +464,11 @@
       <c r="D2" s="3"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>15</v>
+      <c r="A3" s="2">
+        <v>1056123120</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>2</v>
@@ -512,11 +476,11 @@
       <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>16</v>
+      <c r="A4" s="2">
+        <v>1056123121</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>4</v>
@@ -524,11 +488,11 @@
       <c r="D4" s="3"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>17</v>
+      <c r="A5" s="2">
+        <v>1056123122</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>5</v>
@@ -536,11 +500,11 @@
       <c r="D5" s="3"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>18</v>
+      <c r="A6" s="2">
+        <v>1056123123</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>6</v>
@@ -548,11 +512,11 @@
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>19</v>
+      <c r="A7" s="2">
+        <v>1056123124</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>7</v>
@@ -560,11 +524,11 @@
       <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>20</v>
+      <c r="A8" s="2">
+        <v>1056123125</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>8</v>
@@ -572,11 +536,11 @@
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>21</v>
+      <c r="A9" s="2">
+        <v>1056123126</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>9</v>
@@ -584,11 +548,11 @@
       <c r="D9" s="3"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>22</v>
+      <c r="A10" s="2">
+        <v>1056123127</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>10</v>
@@ -596,11 +560,11 @@
       <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>23</v>
+      <c r="A11" s="2">
+        <v>1056123128</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>11</v>
@@ -608,11 +572,11 @@
       <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>24</v>
+      <c r="A12" s="2">
+        <v>1056123129</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>12</v>
@@ -620,11 +584,11 @@
       <c r="D12" s="3"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>25</v>
+      <c r="A13" s="2">
+        <v>1056123130</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>13</v>
